--- a/paper/screening.xlsx
+++ b/paper/screening.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WL961KX\Private\MSc\Thesis\Systematic Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83346E1D-3A17-4774-8E89-F6FC86DAD508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA9221B-CDC6-4153-B579-6560372AA4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Screening" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={A23B929B-1F88-420C-A8C6-6233EE7C8E8F}</author>
+    <author>tc={6EEC5CFA-B222-4CA3-925C-04E536C2B580}</author>
     <author>tc={373F542D-AF71-4660-BEC6-02DF05EBA826}</author>
     <author>tc={FFFA284C-776A-4C26-BD00-4AB344B57E16}</author>
     <author>tc={D62BB6DA-948E-4A28-B6FB-A4B13EB08F16}</author>
@@ -59,7 +61,6 @@
     <author>tc={241734E3-F744-4D52-B89F-96EB6D3C3153}</author>
     <author>tc={C536C448-E82A-4EDF-9ABA-240EDC0BD618}</author>
     <author>tc={B87D8D32-FF14-4B06-B8C9-9BB3CDF78D6C}</author>
-    <author>tc={EA1EE393-2B0E-40FD-B221-08D0E86D83D0}</author>
     <author>tc={DD6D54C5-6BC1-4E2F-A4DB-141BA1177A6C}</author>
     <author>tc={4F75EA70-DAA7-467B-BD29-1E817F9F74F6}</author>
     <author>tc={5AF726B1-29B7-4FF3-9A28-0B9438A210B6}</author>
@@ -180,7 +181,23 @@
     <author>tc={B371964B-2AAC-4AC9-A5AE-70545583CE99}</author>
   </authors>
   <commentList>
-    <comment ref="V14" authorId="0" shapeId="0" xr:uid="{373F542D-AF71-4660-BEC6-02DF05EBA826}">
+    <comment ref="Q6" authorId="0" shapeId="0" xr:uid="{A23B929B-1F88-420C-A8C6-6233EE7C8E8F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Detailed model specifications (e.g. number of trees in random forest) are not disclosed.</t>
+      </text>
+    </comment>
+    <comment ref="R11" authorId="1" shapeId="0" xr:uid="{6EEC5CFA-B222-4CA3-925C-04E536C2B580}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Grid search on train-val split is mentioned, however target metric used for best hyperparameter combination selection is not disclosed.</t>
+      </text>
+    </comment>
+    <comment ref="V14" authorId="2" shapeId="0" xr:uid="{373F542D-AF71-4660-BEC6-02DF05EBA826}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -188,7 +205,7 @@
     There was only train/test split so we treat these „test” results as dev, since „test” split is not held-out</t>
       </text>
     </comment>
-    <comment ref="M19" authorId="1" shapeId="0" xr:uid="{FFFA284C-776A-4C26-BD00-4AB344B57E16}">
+    <comment ref="M19" authorId="3" shapeId="0" xr:uid="{FFFA284C-776A-4C26-BD00-4AB344B57E16}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -196,7 +213,7 @@
     MFCC features extraction is weakly described (no information regarding audio preprocessing, lack of windowing description)</t>
       </text>
     </comment>
-    <comment ref="O19" authorId="2" shapeId="0" xr:uid="{D62BB6DA-948E-4A28-B6FB-A4B13EB08F16}">
+    <comment ref="O19" authorId="4" shapeId="0" xr:uid="{D62BB6DA-948E-4A28-B6FB-A4B13EB08F16}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -204,7 +221,7 @@
     Partitions disjoint level is not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q19" authorId="3" shapeId="0" xr:uid="{8C615F95-29EE-4A62-9132-7E778EB89ADE}">
+    <comment ref="Q19" authorId="5" shapeId="0" xr:uid="{8C615F95-29EE-4A62-9132-7E778EB89ADE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -212,7 +229,7 @@
     Training details are not disclosed (optimizer, learning rate, number of epochs)</t>
       </text>
     </comment>
-    <comment ref="R19" authorId="4" shapeId="0" xr:uid="{CE57047F-CEF9-41C5-B1EA-3D6BBBB24304}">
+    <comment ref="R19" authorId="6" shapeId="0" xr:uid="{CE57047F-CEF9-41C5-B1EA-3D6BBBB24304}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -220,7 +237,7 @@
     Convergence criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="AC19" authorId="5" shapeId="0" xr:uid="{3831AEEA-9035-4DFC-B6CC-02128C3088CC}">
+    <comment ref="AC19" authorId="7" shapeId="0" xr:uid="{3831AEEA-9035-4DFC-B6CC-02128C3088CC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -228,7 +245,7 @@
     From data preprocessing it’s unclear whether interviewer’s turns are used for the model training</t>
       </text>
     </comment>
-    <comment ref="M21" authorId="6" shapeId="0" xr:uid="{C9DA5871-6241-4670-8E15-94D802DFD5AE}">
+    <comment ref="M21" authorId="8" shapeId="0" xr:uid="{C9DA5871-6241-4670-8E15-94D802DFD5AE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -236,7 +253,7 @@
     Lack of description of validation set preprocessing</t>
       </text>
     </comment>
-    <comment ref="O21" authorId="7" shapeId="0" xr:uid="{D7FD71E6-6DAA-4726-B1AB-0C34320015EF}">
+    <comment ref="O21" authorId="9" shapeId="0" xr:uid="{D7FD71E6-6DAA-4726-B1AB-0C34320015EF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -244,7 +261,7 @@
     Training partition was disjoint into 382 seconds fragments, however validation partition disjoint level is not disclosed</t>
       </text>
     </comment>
-    <comment ref="P21" authorId="8" shapeId="0" xr:uid="{E38BABEB-CFB3-4542-917F-F07BCA21F894}">
+    <comment ref="P21" authorId="10" shapeId="0" xr:uid="{E38BABEB-CFB3-4542-917F-F07BCA21F894}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -252,7 +269,7 @@
     Model hyperparameters are not disclosed (number of layers, dimensionality of each layer, convolutional kernels etc.)</t>
       </text>
     </comment>
-    <comment ref="Q21" authorId="9" shapeId="0" xr:uid="{928F0FE5-2B68-4856-A132-D9FF9659BD2D}">
+    <comment ref="Q21" authorId="11" shapeId="0" xr:uid="{928F0FE5-2B68-4856-A132-D9FF9659BD2D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -260,7 +277,7 @@
     Training details are not disclosed (optimizer, learning rate, number of epochs)</t>
       </text>
     </comment>
-    <comment ref="R21" authorId="10" shapeId="0" xr:uid="{E104377B-C474-4AC8-BB3E-598B9A685AFA}">
+    <comment ref="R21" authorId="12" shapeId="0" xr:uid="{E104377B-C474-4AC8-BB3E-598B9A685AFA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -268,7 +285,7 @@
     Convergence criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="M22" authorId="11" shapeId="0" xr:uid="{84F46DE2-4FAE-4B9B-A300-7DF85859FD98}">
+    <comment ref="M22" authorId="13" shapeId="0" xr:uid="{84F46DE2-4FAE-4B9B-A300-7DF85859FD98}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -276,7 +293,7 @@
     Data preprocessing description is poor and chaotic: „To minimize noise in text data, commonly used words such as "and," "the," and "is" that lack significant meaning are usually eliminated”. For some reason correlation analysis is performed within AVEC 2019 dataset</t>
       </text>
     </comment>
-    <comment ref="O22" authorId="12" shapeId="0" xr:uid="{D6D24D22-5AA6-4156-8903-DC06874882AD}">
+    <comment ref="O22" authorId="14" shapeId="0" xr:uid="{D6D24D22-5AA6-4156-8903-DC06874882AD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -284,7 +301,7 @@
     Partitions disjoint level is not disclosed</t>
       </text>
     </comment>
-    <comment ref="P22" authorId="13" shapeId="0" xr:uid="{680EFC0F-5806-4DB9-952F-B20D65B5730D}">
+    <comment ref="P22" authorId="15" shapeId="0" xr:uid="{680EFC0F-5806-4DB9-952F-B20D65B5730D}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -292,7 +309,7 @@
     Inconsistencies in model description. Autors state extraction of „767 embeddings”, supposedly meaning „767 dimensional embeddings”, hovewer BERT model produces 768-dimensional vectors. Number of LSTM layers is not disclosed. Autoencoder dimensionality is not disclosed </t>
       </text>
     </comment>
-    <comment ref="Q22" authorId="14" shapeId="0" xr:uid="{44A2EE67-55A6-4BC2-90F6-FDA083273580}">
+    <comment ref="Q22" authorId="16" shapeId="0" xr:uid="{44A2EE67-55A6-4BC2-90F6-FDA083273580}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -300,7 +317,7 @@
     Training description lacks details (optimizer, early stopping setting)</t>
       </text>
     </comment>
-    <comment ref="R22" authorId="15" shapeId="0" xr:uid="{136AD2B7-31E1-41BA-8735-96A026829F7A}">
+    <comment ref="R22" authorId="17" shapeId="0" xr:uid="{136AD2B7-31E1-41BA-8735-96A026829F7A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -308,7 +325,7 @@
     Early stopping was used, however description lacks details</t>
       </text>
     </comment>
-    <comment ref="Q24" authorId="16" shapeId="0" xr:uid="{A07125B4-F3CD-4801-BB1B-C5BB99036794}">
+    <comment ref="Q24" authorId="18" shapeId="0" xr:uid="{A07125B4-F3CD-4801-BB1B-C5BB99036794}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -316,7 +333,7 @@
     Training details are not disclosed</t>
       </text>
     </comment>
-    <comment ref="R24" authorId="17" shapeId="0" xr:uid="{919E3660-C35C-41A6-95B6-B281B5E41095}">
+    <comment ref="R24" authorId="19" shapeId="0" xr:uid="{919E3660-C35C-41A6-95B6-B281B5E41095}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -324,7 +341,7 @@
     Convergence criteria for text modality are not disclosed. </t>
       </text>
     </comment>
-    <comment ref="Q37" authorId="18" shapeId="0" xr:uid="{D6594F58-992F-4BF3-95A7-F4A4E2DFCFA9}">
+    <comment ref="Q37" authorId="20" shapeId="0" xr:uid="{D6594F58-992F-4BF3-95A7-F4A4E2DFCFA9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -332,7 +349,7 @@
     Everything was really good except the lack of PV model pretraining process description</t>
       </text>
     </comment>
-    <comment ref="AB39" authorId="19" shapeId="0" xr:uid="{241734E3-F744-4D52-B89F-96EB6D3C3153}">
+    <comment ref="AB39" authorId="21" shapeId="0" xr:uid="{241734E3-F744-4D52-B89F-96EB6D3C3153}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -340,7 +357,7 @@
     No crossval, just repeated (5 times) experiments with different seeds</t>
       </text>
     </comment>
-    <comment ref="V44" authorId="20" shapeId="0" xr:uid="{C536C448-E82A-4EDF-9ABA-240EDC0BD618}">
+    <comment ref="V44" authorId="22" shapeId="0" xr:uid="{C536C448-E82A-4EDF-9ABA-240EDC0BD618}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -348,7 +365,7 @@
     There was only train/test split so we treat these „test” results as dev, since „test” split is not held-out</t>
       </text>
     </comment>
-    <comment ref="V51" authorId="21" shapeId="0" xr:uid="{B87D8D32-FF14-4B06-B8C9-9BB3CDF78D6C}">
+    <comment ref="V51" authorId="23" shapeId="0" xr:uid="{B87D8D32-FF14-4B06-B8C9-9BB3CDF78D6C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -356,23 +373,15 @@
     There are inconsistencies in reported MAE values in tables with ones in the text, therefore we do not include them here</t>
       </text>
     </comment>
-    <comment ref="M52" authorId="22" shapeId="0" xr:uid="{EA1EE393-2B0E-40FD-B221-08D0E86D83D0}">
+    <comment ref="Q52" authorId="24" shapeId="0" xr:uid="{DD6D54C5-6BC1-4E2F-A4DB-141BA1177A6C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Vague description of transcripts preprocessing. It’s not clear whether interviewer prompts are included in the context fed to GPT</t>
+    Prompts are not disclosed.</t>
       </text>
     </comment>
-    <comment ref="Q52" authorId="23" shapeId="0" xr:uid="{DD6D54C5-6BC1-4E2F-A4DB-141BA1177A6C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Prompts are not disclosed, but we put here N/A since the model is not actually trained</t>
-      </text>
-    </comment>
-    <comment ref="O59" authorId="24" shapeId="0" xr:uid="{4F75EA70-DAA7-467B-BD29-1E817F9F74F6}">
+    <comment ref="O59" authorId="25" shapeId="0" xr:uid="{4F75EA70-DAA7-467B-BD29-1E817F9F74F6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -380,7 +389,7 @@
     No clear information on disjoint level. There are mentions of „sentences” but no concise section regarding data preprocessing</t>
       </text>
     </comment>
-    <comment ref="Q59" authorId="25" shapeId="0" xr:uid="{5AF726B1-29B7-4FF3-9A28-0B9438A210B6}">
+    <comment ref="Q59" authorId="26" shapeId="0" xr:uid="{5AF726B1-29B7-4FF3-9A28-0B9438A210B6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -388,7 +397,7 @@
     No description of the final model archtecture. There are mentions of SVM and DT but nothing about link between them</t>
       </text>
     </comment>
-    <comment ref="I60" authorId="26" shapeId="0" xr:uid="{DE069F52-8C4D-49C6-A026-295FF162079F}">
+    <comment ref="I60" authorId="27" shapeId="0" xr:uid="{DE069F52-8C4D-49C6-A026-295FF162079F}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -400,7 +409,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="M65" authorId="27" shapeId="0" xr:uid="{C12E0521-C4AD-4E57-8ACA-D31644BFB1A7}">
+    <comment ref="M65" authorId="28" shapeId="0" xr:uid="{C12E0521-C4AD-4E57-8ACA-D31644BFB1A7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -408,7 +417,7 @@
     Weak description of data preprocesing</t>
       </text>
     </comment>
-    <comment ref="O65" authorId="28" shapeId="0" xr:uid="{D3EB1694-FCB7-4DBC-9338-25A27F838D40}">
+    <comment ref="O65" authorId="29" shapeId="0" xr:uid="{D3EB1694-FCB7-4DBC-9338-25A27F838D40}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -416,7 +425,7 @@
     Unclear partitions disjoint level</t>
       </text>
     </comment>
-    <comment ref="P65" authorId="29" shapeId="0" xr:uid="{4F827CA5-96E1-4D9A-9530-E38196E4A45C}">
+    <comment ref="P65" authorId="30" shapeId="0" xr:uid="{4F827CA5-96E1-4D9A-9530-E38196E4A45C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -424,7 +433,7 @@
     Very chaotic desctiption of models used per modality and their ensemble</t>
       </text>
     </comment>
-    <comment ref="M127" authorId="30" shapeId="0" xr:uid="{D42D618F-E3CE-4EC1-9EE4-A4EAED30C66E}">
+    <comment ref="M127" authorId="31" shapeId="0" xr:uid="{D42D618F-E3CE-4EC1-9EE4-A4EAED30C66E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -432,7 +441,7 @@
     Data preprocessing is not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q127" authorId="31" shapeId="0" xr:uid="{18A7B5B6-8AFD-4397-B747-6A4EE3991145}">
+    <comment ref="Q127" authorId="32" shapeId="0" xr:uid="{18A7B5B6-8AFD-4397-B747-6A4EE3991145}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -440,7 +449,7 @@
     Learning rate decay is not described. Cross-validation is performed on an unknown partition</t>
       </text>
     </comment>
-    <comment ref="R127" authorId="32" shapeId="0" xr:uid="{B7576B8A-6228-4FB1-B604-631C9A8EE7AB}">
+    <comment ref="R127" authorId="33" shapeId="0" xr:uid="{B7576B8A-6228-4FB1-B604-631C9A8EE7AB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -448,7 +457,7 @@
     The description of best model selection is vague: „As shown in Table V, we give the hyperparameters used in our experiments and tune the hyperparameters via grid search in the validation set, at meantime we train all the learning models using 5-cross validation.„ It’s unclear on which subset the cross-validation is performed</t>
       </text>
     </comment>
-    <comment ref="U127" authorId="33" shapeId="0" xr:uid="{FCB1BEB6-4975-4F57-8E90-64FBDDFCC56F}">
+    <comment ref="U127" authorId="34" shapeId="0" xr:uid="{FCB1BEB6-4975-4F57-8E90-64FBDDFCC56F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -456,7 +465,7 @@
     Reported results regard unknown partiion</t>
       </text>
     </comment>
-    <comment ref="I133" authorId="34" shapeId="0" xr:uid="{FF77D7A8-49AA-4492-BCD1-E1C5C57C4A0C}">
+    <comment ref="I133" authorId="35" shapeId="0" xr:uid="{FF77D7A8-49AA-4492-BCD1-E1C5C57C4A0C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -465,7 +474,7 @@
 (2023)</t>
       </text>
     </comment>
-    <comment ref="I134" authorId="35" shapeId="0" xr:uid="{5F3F83A7-B7F4-4A10-91A5-338772EF050A}">
+    <comment ref="I134" authorId="36" shapeId="0" xr:uid="{5F3F83A7-B7F4-4A10-91A5-338772EF050A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -475,7 +484,7 @@
 The only difference is additional preprocessing of samples</t>
       </text>
     </comment>
-    <comment ref="I135" authorId="36" shapeId="0" xr:uid="{3E03AF45-57E1-4BF5-BF08-ADB13A29E840}">
+    <comment ref="I135" authorId="37" shapeId="0" xr:uid="{3E03AF45-57E1-4BF5-BF08-ADB13A29E840}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -485,7 +494,7 @@
 Same authors, same year of publication (2020)</t>
       </text>
     </comment>
-    <comment ref="I137" authorId="37" shapeId="0" xr:uid="{E8361CB6-D713-4A2A-9821-68FDFD14E50A}">
+    <comment ref="I137" authorId="38" shapeId="0" xr:uid="{E8361CB6-D713-4A2A-9821-68FDFD14E50A}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -499,7 +508,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="Q139" authorId="38" shapeId="0" xr:uid="{239E56BD-F310-4503-8A94-CAB4F2DEE74F}">
+    <comment ref="Q139" authorId="39" shapeId="0" xr:uid="{239E56BD-F310-4503-8A94-CAB4F2DEE74F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -509,7 +518,7 @@
     No information on hyperparameters tuned</t>
       </text>
     </comment>
-    <comment ref="U139" authorId="39" shapeId="0" xr:uid="{2E35A4BF-C58C-47C5-8D99-05F190E38934}">
+    <comment ref="U139" authorId="40" shapeId="0" xr:uid="{2E35A4BF-C58C-47C5-8D99-05F190E38934}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -517,7 +526,7 @@
     We suppose that results are reported for the validation (dev) set, however it is not disclosed anywhere in paper</t>
       </text>
     </comment>
-    <comment ref="V139" authorId="40" shapeId="0" xr:uid="{5CBA867F-F162-4C65-A8C5-83AF3FBFFD78}">
+    <comment ref="V139" authorId="41" shapeId="0" xr:uid="{5CBA867F-F162-4C65-A8C5-83AF3FBFFD78}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -525,7 +534,7 @@
     We suppose that results are reported for the validation (dev) set, however it is not disclosed anywhere in paper</t>
       </text>
     </comment>
-    <comment ref="N142" authorId="41" shapeId="0" xr:uid="{70C958AC-3EA8-443A-9F7E-3A78A929E3D9}">
+    <comment ref="N142" authorId="42" shapeId="0" xr:uid="{70C958AC-3EA8-443A-9F7E-3A78A929E3D9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -533,7 +542,7 @@
     No information regarding data partitioning. There’s a mention of a „standard protocol” but we did’t find obvious data partitioning scheme there</t>
       </text>
     </comment>
-    <comment ref="P142" authorId="42" shapeId="0" xr:uid="{C87EB2D5-8870-472A-94CE-643E985FD019}">
+    <comment ref="P142" authorId="43" shapeId="0" xr:uid="{C87EB2D5-8870-472A-94CE-643E985FD019}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -541,7 +550,7 @@
     No information regarding threshold used for selection a number of layers</t>
       </text>
     </comment>
-    <comment ref="Q142" authorId="43" shapeId="0" xr:uid="{04B90ADB-08C2-48C3-9E35-718DB089F610}">
+    <comment ref="Q142" authorId="44" shapeId="0" xr:uid="{04B90ADB-08C2-48C3-9E35-718DB089F610}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -549,7 +558,7 @@
     Some of the prompts are not disclosed, but we put here N/A since the model is not actually trained</t>
       </text>
     </comment>
-    <comment ref="I143" authorId="44" shapeId="0" xr:uid="{232B2CFA-B534-497F-9CB0-64ADF6267D62}">
+    <comment ref="I143" authorId="45" shapeId="0" xr:uid="{232B2CFA-B534-497F-9CB0-64ADF6267D62}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -559,7 +568,7 @@
 Hovewer this work was published earlier we still consider this as not introducing novelty.</t>
       </text>
     </comment>
-    <comment ref="M144" authorId="45" shapeId="0" xr:uid="{1DDD1A0A-4C59-4F1D-887A-466C2DDAC19B}">
+    <comment ref="M144" authorId="46" shapeId="0" xr:uid="{1DDD1A0A-4C59-4F1D-887A-466C2DDAC19B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -567,7 +576,7 @@
     Vague description of data preprocessing (oversampling, irrelevant data filtering, mel spectrogram calculation)</t>
       </text>
     </comment>
-    <comment ref="O144" authorId="46" shapeId="0" xr:uid="{E26C94BA-ED51-4166-8F00-00ED7962D6DE}">
+    <comment ref="O144" authorId="47" shapeId="0" xr:uid="{E26C94BA-ED51-4166-8F00-00ED7962D6DE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -575,7 +584,7 @@
     It’s not clear at which level partitions are disjoint</t>
       </text>
     </comment>
-    <comment ref="R144" authorId="47" shapeId="0" xr:uid="{B930B21D-44A8-475E-B41A-BB358D9639A7}">
+    <comment ref="R144" authorId="48" shapeId="0" xr:uid="{B930B21D-44A8-475E-B41A-BB358D9639A7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -583,7 +592,7 @@
     No convergence criteria applied. Model was trained for fixed amount of epochs</t>
       </text>
     </comment>
-    <comment ref="AB150" authorId="48" shapeId="0" xr:uid="{50E07006-FBD2-4CE1-B0A3-606576B51666}">
+    <comment ref="AB150" authorId="49" shapeId="0" xr:uid="{50E07006-FBD2-4CE1-B0A3-606576B51666}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -591,7 +600,7 @@
     Crossval is performed in ablation study and results are: testMAE=3,52; testRMSE=4,32</t>
       </text>
     </comment>
-    <comment ref="M151" authorId="49" shapeId="0" xr:uid="{BA7D8F85-C321-427E-BB22-96879C8CD266}">
+    <comment ref="M151" authorId="50" shapeId="0" xr:uid="{BA7D8F85-C321-427E-BB22-96879C8CD266}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -599,7 +608,7 @@
     It’s unclear how 512 ResNet18 features were extracted from various timeseries spatial data</t>
       </text>
     </comment>
-    <comment ref="P151" authorId="50" shapeId="0" xr:uid="{94325C28-0555-4441-BBA4-D8DCB054C488}">
+    <comment ref="P151" authorId="51" shapeId="0" xr:uid="{94325C28-0555-4441-BBA4-D8DCB054C488}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -607,7 +616,7 @@
     Architecture is over-complicated and taking into consideration issues with data preprocessing and training details we do not delve into analyzing the proposed architecture</t>
       </text>
     </comment>
-    <comment ref="Q151" authorId="51" shapeId="0" xr:uid="{DAB292EC-01D7-454E-AA87-615A8598FE27}">
+    <comment ref="Q151" authorId="52" shapeId="0" xr:uid="{DAB292EC-01D7-454E-AA87-615A8598FE27}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -615,7 +624,7 @@
     Lack of training-related details (number of epochs, optimizer)</t>
       </text>
     </comment>
-    <comment ref="R151" authorId="52" shapeId="0" xr:uid="{6C749010-EDC1-4C8E-9FA8-809AD6D15563}">
+    <comment ref="R151" authorId="53" shapeId="0" xr:uid="{6C749010-EDC1-4C8E-9FA8-809AD6D15563}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -623,7 +632,7 @@
     Convergence criteria are not disclosed. </t>
       </text>
     </comment>
-    <comment ref="M155" authorId="53" shapeId="0" xr:uid="{2D0465DD-01ED-4968-B70D-F5AFE1CE25E5}">
+    <comment ref="M155" authorId="54" shapeId="0" xr:uid="{2D0465DD-01ED-4968-B70D-F5AFE1CE25E5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -631,7 +640,7 @@
     Exhaustive description of the data preprocessing</t>
       </text>
     </comment>
-    <comment ref="P155" authorId="54" shapeId="0" xr:uid="{B2D44447-2C3E-4FD9-8E11-0F7603F8B958}">
+    <comment ref="P155" authorId="55" shapeId="0" xr:uid="{B2D44447-2C3E-4FD9-8E11-0F7603F8B958}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -639,7 +648,7 @@
     Equation 1 presents operations performed on input in a wrong order</t>
       </text>
     </comment>
-    <comment ref="R155" authorId="55" shapeId="0" xr:uid="{226F52C7-179E-41B6-A6A9-ED3A8A1731AE}">
+    <comment ref="R155" authorId="56" shapeId="0" xr:uid="{226F52C7-179E-41B6-A6A9-ED3A8A1731AE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -647,7 +656,7 @@
     Ablation study is performed on unknown data partition. Best model selection criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="M159" authorId="56" shapeId="0" xr:uid="{0E399AB5-F9A7-407D-A208-4A621FC75B15}">
+    <comment ref="M159" authorId="57" shapeId="0" xr:uid="{0E399AB5-F9A7-407D-A208-4A621FC75B15}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -655,7 +664,7 @@
     No information regarding including interviewer turns in transcripts</t>
       </text>
     </comment>
-    <comment ref="Q159" authorId="57" shapeId="0" xr:uid="{1D26D19A-A93C-48F6-9EB4-99E66DEBC54F}">
+    <comment ref="Q159" authorId="58" shapeId="0" xr:uid="{1D26D19A-A93C-48F6-9EB4-99E66DEBC54F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -663,7 +672,7 @@
     Authors use multitask objective, predicting binary label and phq8 score simultaneously</t>
       </text>
     </comment>
-    <comment ref="U159" authorId="58" shapeId="0" xr:uid="{0B171D47-59C1-4635-9E12-DC01C92A2163}">
+    <comment ref="U159" authorId="59" shapeId="0" xr:uid="{0B171D47-59C1-4635-9E12-DC01C92A2163}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -671,7 +680,7 @@
     Here we include reported averages for the hparams combination which according to the authors produced best model - fastText with mean pooling</t>
       </text>
     </comment>
-    <comment ref="N161" authorId="59" shapeId="0" xr:uid="{25A8D58B-D5D2-457C-94D7-7CE4EA476FBE}">
+    <comment ref="N161" authorId="60" shapeId="0" xr:uid="{25A8D58B-D5D2-457C-94D7-7CE4EA476FBE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -679,7 +688,7 @@
     Data partitioning is not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q161" authorId="60" shapeId="0" xr:uid="{99DC417D-BEEC-411B-A77C-301FCA403E83}">
+    <comment ref="Q161" authorId="61" shapeId="0" xr:uid="{99DC417D-BEEC-411B-A77C-301FCA403E83}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -687,7 +696,7 @@
     Training details are not disclosed</t>
       </text>
     </comment>
-    <comment ref="U161" authorId="61" shapeId="0" xr:uid="{C7F77C37-1972-4514-ABD4-3E233A142C77}">
+    <comment ref="U161" authorId="62" shapeId="0" xr:uid="{C7F77C37-1972-4514-ABD4-3E233A142C77}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -695,7 +704,7 @@
     Reported results regard unknown partition, therefore are not included in our table</t>
       </text>
     </comment>
-    <comment ref="Q162" authorId="62" shapeId="0" xr:uid="{B2D55262-5DAC-40DD-8409-2A6FDA7E4656}">
+    <comment ref="Q162" authorId="63" shapeId="0" xr:uid="{B2D55262-5DAC-40DD-8409-2A6FDA7E4656}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -705,7 +714,7 @@
     Multitask training</t>
       </text>
     </comment>
-    <comment ref="X162" authorId="63" shapeId="0" xr:uid="{29098707-59E9-407C-B0AC-D72B9D11FB7C}">
+    <comment ref="X162" authorId="64" shapeId="0" xr:uid="{29098707-59E9-407C-B0AC-D72B9D11FB7C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -713,7 +722,7 @@
     We assume that reported values regard test set, however this is not explicitly stated in the paper</t>
       </text>
     </comment>
-    <comment ref="I164" authorId="64" shapeId="0" xr:uid="{17C38BA3-180B-4B77-99AC-549891FE7CA6}">
+    <comment ref="I164" authorId="65" shapeId="0" xr:uid="{17C38BA3-180B-4B77-99AC-549891FE7CA6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -723,7 +732,7 @@
 Training models on QA pairs was also explored in previous work in this field</t>
       </text>
     </comment>
-    <comment ref="M168" authorId="65" shapeId="0" xr:uid="{7E22DCD6-AB09-44C8-A2E7-5E467C0C226C}">
+    <comment ref="M168" authorId="66" shapeId="0" xr:uid="{7E22DCD6-AB09-44C8-A2E7-5E467C0C226C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -731,7 +740,7 @@
     Described video preprocessing is not applicable to DAIC-WOZ dataset, since the features are already extracted from video. BoW extraction from transcripts is vague</t>
       </text>
     </comment>
-    <comment ref="P168" authorId="66" shapeId="0" xr:uid="{BA533ADF-4DF1-430B-B73B-E068D4AAD557}">
+    <comment ref="P168" authorId="67" shapeId="0" xr:uid="{BA533ADF-4DF1-430B-B73B-E068D4AAD557}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -739,7 +748,7 @@
     Exact dimensionalities and number of layers is not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q168" authorId="67" shapeId="0" xr:uid="{6DEA035D-04F0-4E8A-8177-9FECB41806AA}">
+    <comment ref="Q168" authorId="68" shapeId="0" xr:uid="{6DEA035D-04F0-4E8A-8177-9FECB41806AA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -747,7 +756,7 @@
     Training-related details are not disclosed (optimizer, learning rate, number of epochs etc)</t>
       </text>
     </comment>
-    <comment ref="R168" authorId="68" shapeId="0" xr:uid="{7732DB7C-7EA3-4C92-87E5-D08E73B3E315}">
+    <comment ref="R168" authorId="69" shapeId="0" xr:uid="{7732DB7C-7EA3-4C92-87E5-D08E73B3E315}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -755,7 +764,7 @@
     Convergence and best model selection criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="M169" authorId="69" shapeId="0" xr:uid="{F3F88B72-07F2-4E31-ACE5-BB60B29C3D39}">
+    <comment ref="M169" authorId="70" shapeId="0" xr:uid="{F3F88B72-07F2-4E31-ACE5-BB60B29C3D39}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -763,7 +772,7 @@
     No information regarding data preprocessing. It’s unclear how 767 BERT embeddings were extracted from transcripts and why they were identified as essential</t>
       </text>
     </comment>
-    <comment ref="O169" authorId="70" shapeId="0" xr:uid="{13D0120B-D25F-4D2F-A3AA-791BDE601FB3}">
+    <comment ref="O169" authorId="71" shapeId="0" xr:uid="{13D0120B-D25F-4D2F-A3AA-791BDE601FB3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -771,7 +780,7 @@
     Partitions disjoint level is not disclosed</t>
       </text>
     </comment>
-    <comment ref="P169" authorId="71" shapeId="0" xr:uid="{C54D3268-9963-4670-885A-164043CBF2C8}">
+    <comment ref="P169" authorId="72" shapeId="0" xr:uid="{C54D3268-9963-4670-885A-164043CBF2C8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -779,7 +788,7 @@
     Chaotic description of the model</t>
       </text>
     </comment>
-    <comment ref="Q169" authorId="72" shapeId="0" xr:uid="{9EF6F554-393B-485D-9E3E-3886A063C914}">
+    <comment ref="Q169" authorId="73" shapeId="0" xr:uid="{9EF6F554-393B-485D-9E3E-3886A063C914}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -787,7 +796,7 @@
     Number of epochs and optimizer are not disclosed</t>
       </text>
     </comment>
-    <comment ref="R169" authorId="73" shapeId="0" xr:uid="{6AD423DF-21DA-4C6D-953E-13FEC4D19F3B}">
+    <comment ref="R169" authorId="74" shapeId="0" xr:uid="{6AD423DF-21DA-4C6D-953E-13FEC4D19F3B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -795,7 +804,7 @@
     Convergence criteria are not disclosed.</t>
       </text>
     </comment>
-    <comment ref="U169" authorId="74" shapeId="0" xr:uid="{403ACB70-1F41-4813-80CF-8874860DE1BA}">
+    <comment ref="U169" authorId="75" shapeId="0" xr:uid="{403ACB70-1F41-4813-80CF-8874860DE1BA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -803,7 +812,7 @@
     We suspect that these results are falsely reported. MAE is too small for R2 which is less than 0.7. Also comparing this to other quality works reported results do not look realistic</t>
       </text>
     </comment>
-    <comment ref="O170" authorId="75" shapeId="0" xr:uid="{E34C4837-E4DE-47AC-BA53-727154261DBD}">
+    <comment ref="O170" authorId="76" shapeId="0" xr:uid="{E34C4837-E4DE-47AC-BA53-727154261DBD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -811,7 +820,7 @@
     Unclear partitions disjoint level</t>
       </text>
     </comment>
-    <comment ref="Q170" authorId="76" shapeId="0" xr:uid="{BAB18B65-4E77-45A3-9A5B-0CE1BC9C8FDD}">
+    <comment ref="Q170" authorId="77" shapeId="0" xr:uid="{BAB18B65-4E77-45A3-9A5B-0CE1BC9C8FDD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -819,7 +828,7 @@
     Number of epochs for multimodal model training is not disclosed</t>
       </text>
     </comment>
-    <comment ref="M171" authorId="77" shapeId="0" xr:uid="{8175C45F-5957-4219-BD23-758D4CDFBAE7}">
+    <comment ref="M171" authorId="78" shapeId="0" xr:uid="{8175C45F-5957-4219-BD23-758D4CDFBAE7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -827,7 +836,7 @@
     Feature extraction for audio and video modalities is weakly described</t>
       </text>
     </comment>
-    <comment ref="O171" authorId="78" shapeId="0" xr:uid="{0752A1ED-0987-4831-AD83-A7480440D908}">
+    <comment ref="O171" authorId="79" shapeId="0" xr:uid="{0752A1ED-0987-4831-AD83-A7480440D908}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -835,7 +844,7 @@
     Partitions disjoint level is not clearly disclosed</t>
       </text>
     </comment>
-    <comment ref="Q171" authorId="79" shapeId="0" xr:uid="{7793AD39-F74F-4452-BD36-4ED781EC6505}">
+    <comment ref="Q171" authorId="80" shapeId="0" xr:uid="{7793AD39-F74F-4452-BD36-4ED781EC6505}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -843,7 +852,7 @@
     Training details are not disclosed</t>
       </text>
     </comment>
-    <comment ref="U171" authorId="80" shapeId="0" xr:uid="{16357A52-4A00-4324-8A0C-3280E49B5A6A}">
+    <comment ref="U171" authorId="81" shapeId="0" xr:uid="{16357A52-4A00-4324-8A0C-3280E49B5A6A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -851,7 +860,7 @@
     Reported results regard unknown partition</t>
       </text>
     </comment>
-    <comment ref="P173" authorId="81" shapeId="0" xr:uid="{FBE253FE-3884-4D6F-8EC4-64F580608B77}">
+    <comment ref="P173" authorId="82" shapeId="0" xr:uid="{FBE253FE-3884-4D6F-8EC4-64F580608B77}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -859,7 +868,7 @@
     Tree-based feature selection algorithm is not described. Lambda layer is not described. Parametrization is not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q173" authorId="82" shapeId="0" xr:uid="{B25B2ED6-91B3-44C9-8847-174EE6EAB38A}">
+    <comment ref="Q173" authorId="83" shapeId="0" xr:uid="{B25B2ED6-91B3-44C9-8847-174EE6EAB38A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -867,7 +876,7 @@
     Text embedding finetuning on conversational data is not disclosed. Lack of training details regarding audio, visual an multi- modal models. Hyperparameters tuned are not disclosed</t>
       </text>
     </comment>
-    <comment ref="R173" authorId="83" shapeId="0" xr:uid="{6ECCA042-5ACE-4B4D-AB03-B8CE582ED431}">
+    <comment ref="R173" authorId="84" shapeId="0" xr:uid="{6ECCA042-5ACE-4B4D-AB03-B8CE582ED431}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -875,7 +884,7 @@
     Final model selection criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="P175" authorId="84" shapeId="0" xr:uid="{DA2785B7-03AB-4BF7-81D1-C2692755B205}">
+    <comment ref="P175" authorId="85" shapeId="0" xr:uid="{DA2785B7-03AB-4BF7-81D1-C2692755B205}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -883,7 +892,7 @@
     Exact architecture with number of BiLSTM layers is not disclosed (hyperparams was tuned, but the best combination is not reported)</t>
       </text>
     </comment>
-    <comment ref="R175" authorId="85" shapeId="0" xr:uid="{D956A544-2B20-45A1-A0B1-3AEC94DC60B2}">
+    <comment ref="R175" authorId="86" shapeId="0" xr:uid="{D956A544-2B20-45A1-A0B1-3AEC94DC60B2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -891,7 +900,7 @@
     Hyperparameter tuning was performed, however best model selection criteria are not disclosed. Convergence criteria are vague: „[...] an early-stopping criterion of 0.001 threshold over a maximum epoch of 100 [...]”</t>
       </text>
     </comment>
-    <comment ref="M176" authorId="86" shapeId="0" xr:uid="{D235CE31-05BC-4E6A-91CD-7AFEDC1FDEA0}">
+    <comment ref="M176" authorId="87" shapeId="0" xr:uid="{D235CE31-05BC-4E6A-91CD-7AFEDC1FDEA0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -899,7 +908,7 @@
     Described data preprocessing is not applicable to DAIC-WOZ dataset. It is also unclear whether audio features include interviewer utterances. Description of dictionaries composition from BERT is vague</t>
       </text>
     </comment>
-    <comment ref="Q176" authorId="87" shapeId="0" xr:uid="{EDD049C4-92CE-402F-8933-06B5B39FC972}">
+    <comment ref="Q176" authorId="88" shapeId="0" xr:uid="{EDD049C4-92CE-402F-8933-06B5B39FC972}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -907,7 +916,7 @@
     Number of training epochs is not disclosed</t>
       </text>
     </comment>
-    <comment ref="R176" authorId="88" shapeId="0" xr:uid="{77B1DA13-8310-45D6-B3BB-EB22D3BD4912}">
+    <comment ref="R176" authorId="89" shapeId="0" xr:uid="{77B1DA13-8310-45D6-B3BB-EB22D3BD4912}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -915,7 +924,7 @@
     Hyperparameter tuning was performed, however best model selection criteria are not disclosed: „To determine the value of N in Fig. 1, we conduct multiple experiments.”</t>
       </text>
     </comment>
-    <comment ref="P180" authorId="89" shapeId="0" xr:uid="{454AD9B6-53C4-40C3-9F62-83DDE9E4A4B8}">
+    <comment ref="P180" authorId="90" shapeId="0" xr:uid="{454AD9B6-53C4-40C3-9F62-83DDE9E4A4B8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -923,7 +932,7 @@
     Architecture is overcomplicated and considering issues in training description and final model selection we do not extract the model description</t>
       </text>
     </comment>
-    <comment ref="Q180" authorId="90" shapeId="0" xr:uid="{A6EF5086-DFF6-4ED0-8D8F-CBC2B2AEC7AA}">
+    <comment ref="Q180" authorId="91" shapeId="0" xr:uid="{A6EF5086-DFF6-4ED0-8D8F-CBC2B2AEC7AA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -931,7 +940,7 @@
     It is unclear whether authors use gradient checkpointing with parameters update once every 25 epochs or they mean something else: „We perform updates every 25 epochs, with a batch size of 8 [...]”</t>
       </text>
     </comment>
-    <comment ref="R180" authorId="91" shapeId="0" xr:uid="{52FEB434-B4C2-45AC-971B-0BAEAA129D25}">
+    <comment ref="R180" authorId="92" shapeId="0" xr:uid="{52FEB434-B4C2-45AC-971B-0BAEAA129D25}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -939,7 +948,7 @@
     Hyperparameter tuning is mentioned, hovewer best model selection criteria are not provided</t>
       </text>
     </comment>
-    <comment ref="U180" authorId="92" shapeId="0" xr:uid="{3AA2E6B0-D7C6-4F5B-A0CB-6BC79D420009}">
+    <comment ref="U180" authorId="93" shapeId="0" xr:uid="{3AA2E6B0-D7C6-4F5B-A0CB-6BC79D420009}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -947,7 +956,7 @@
     Reported results regard unknown partition, however we might assume that it is was test set</t>
       </text>
     </comment>
-    <comment ref="AA180" authorId="93" shapeId="0" xr:uid="{BD432027-419A-443B-831C-571E2879A436}">
+    <comment ref="AA180" authorId="94" shapeId="0" xr:uid="{BD432027-419A-443B-831C-571E2879A436}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -955,7 +964,7 @@
     Repository is empty</t>
       </text>
     </comment>
-    <comment ref="I181" authorId="94" shapeId="0" xr:uid="{7CF707E3-4321-44E6-8419-305986DE3066}">
+    <comment ref="I181" authorId="95" shapeId="0" xr:uid="{7CF707E3-4321-44E6-8419-305986DE3066}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -968,7 +977,7 @@
 Same authors, all papers published in Oct 2017</t>
       </text>
     </comment>
-    <comment ref="I185" authorId="95" shapeId="0" xr:uid="{010B2439-94B1-4B52-B2A6-F6574274F4C3}">
+    <comment ref="I185" authorId="96" shapeId="0" xr:uid="{010B2439-94B1-4B52-B2A6-F6574274F4C3}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -979,7 +988,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="M186" authorId="96" shapeId="0" xr:uid="{BCB79246-6102-45B6-BA5A-B994BCB3728F}">
+    <comment ref="M186" authorId="97" shapeId="0" xr:uid="{BCB79246-6102-45B6-BA5A-B994BCB3728F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -987,7 +996,7 @@
     Data preprocessing for each modality is not described. Graph construction process from data is unclear</t>
       </text>
     </comment>
-    <comment ref="N186" authorId="97" shapeId="0" xr:uid="{682A370B-46C7-4C32-859C-6B3D8AEA073C}">
+    <comment ref="N186" authorId="98" shapeId="0" xr:uid="{682A370B-46C7-4C32-859C-6B3D8AEA073C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -995,7 +1004,7 @@
     Data partitioning is not disclosed</t>
       </text>
     </comment>
-    <comment ref="O186" authorId="98" shapeId="0" xr:uid="{7BFC5B8C-3EAD-4D37-9820-C691EAFCEEB7}">
+    <comment ref="O186" authorId="99" shapeId="0" xr:uid="{7BFC5B8C-3EAD-4D37-9820-C691EAFCEEB7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1003,7 +1012,7 @@
     Partitions disjoint level does not result from graph construction process</t>
       </text>
     </comment>
-    <comment ref="Q186" authorId="99" shapeId="0" xr:uid="{0180D274-815C-40FC-944D-5C362B36EA51}">
+    <comment ref="Q186" authorId="100" shapeId="0" xr:uid="{0180D274-815C-40FC-944D-5C362B36EA51}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1011,7 +1020,7 @@
     Authors probably confuse lambda (learning rate) with Adam beta1 and beta2 parameters. Training is performed on an unknown partition</t>
       </text>
     </comment>
-    <comment ref="U186" authorId="100" shapeId="0" xr:uid="{1A393B53-6B5E-4E2C-A97F-92281931E5DC}">
+    <comment ref="U186" authorId="101" shapeId="0" xr:uid="{1A393B53-6B5E-4E2C-A97F-92281931E5DC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1019,7 +1028,7 @@
     Reported results regard unknown partition</t>
       </text>
     </comment>
-    <comment ref="N188" authorId="101" shapeId="0" xr:uid="{23C80023-4329-4691-8C41-9AB9E1940322}">
+    <comment ref="N188" authorId="102" shapeId="0" xr:uid="{23C80023-4329-4691-8C41-9AB9E1940322}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1027,7 +1036,7 @@
     Data partitioning is not disclosed</t>
       </text>
     </comment>
-    <comment ref="O188" authorId="102" shapeId="0" xr:uid="{81A4A647-9EE2-4F26-AC32-DF193C9CCC3E}">
+    <comment ref="O188" authorId="103" shapeId="0" xr:uid="{81A4A647-9EE2-4F26-AC32-DF193C9CCC3E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1035,7 +1044,7 @@
     Partitions disjoint level is not disclosed</t>
       </text>
     </comment>
-    <comment ref="P188" authorId="103" shapeId="0" xr:uid="{EA2A0425-1D5B-4FC2-9554-F9A3D5FB5EAE}">
+    <comment ref="P188" authorId="104" shapeId="0" xr:uid="{EA2A0425-1D5B-4FC2-9554-F9A3D5FB5EAE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1043,7 +1052,7 @@
     Details regarding model are not disclosed (e.g. number of layers)</t>
       </text>
     </comment>
-    <comment ref="Q188" authorId="104" shapeId="0" xr:uid="{987C1560-5D37-4B0A-9715-4D8700202047}">
+    <comment ref="Q188" authorId="105" shapeId="0" xr:uid="{987C1560-5D37-4B0A-9715-4D8700202047}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1051,7 +1060,7 @@
     Training process is poorly described</t>
       </text>
     </comment>
-    <comment ref="R188" authorId="105" shapeId="0" xr:uid="{BF675BA8-A443-41CE-9A93-F92C533AEF11}">
+    <comment ref="R188" authorId="106" shapeId="0" xr:uid="{BF675BA8-A443-41CE-9A93-F92C533AEF11}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1059,7 +1068,7 @@
     Lack of convergence criteria</t>
       </text>
     </comment>
-    <comment ref="U188" authorId="106" shapeId="0" xr:uid="{4055D0AB-C609-43D5-87A5-980A1F5E0512}">
+    <comment ref="U188" authorId="107" shapeId="0" xr:uid="{4055D0AB-C609-43D5-87A5-980A1F5E0512}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1067,7 +1076,7 @@
     Reported results regard unknown partition</t>
       </text>
     </comment>
-    <comment ref="Q194" authorId="107" shapeId="0" xr:uid="{B55FB8D9-145D-4872-B6CA-F6DF1EFD5256}">
+    <comment ref="Q194" authorId="108" shapeId="0" xr:uid="{B55FB8D9-145D-4872-B6CA-F6DF1EFD5256}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1075,7 +1084,7 @@
     Training-related details are not fully disclosed (number of epochs, best hyperparameters setting)</t>
       </text>
     </comment>
-    <comment ref="R194" authorId="108" shapeId="0" xr:uid="{0BC9EC53-3D5C-4A1D-AA9A-0C63FBAC85E4}">
+    <comment ref="R194" authorId="109" shapeId="0" xr:uid="{0BC9EC53-3D5C-4A1D-AA9A-0C63FBAC85E4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1083,7 +1092,7 @@
     Convergence and best model selection criteria are not disclosed.  </t>
       </text>
     </comment>
-    <comment ref="Q206" authorId="109" shapeId="0" xr:uid="{544DC78A-AF99-4622-B528-719182482E72}">
+    <comment ref="Q206" authorId="110" shapeId="0" xr:uid="{544DC78A-AF99-4622-B528-719182482E72}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1091,7 +1100,7 @@
     Lack of training-related details (learning rate, dropout, number of epochs). Tuned hyperparameters are not disclosed</t>
       </text>
     </comment>
-    <comment ref="R206" authorId="110" shapeId="0" xr:uid="{9F468C17-4238-4301-B5A6-B6CF18C1B320}">
+    <comment ref="R206" authorId="111" shapeId="0" xr:uid="{9F468C17-4238-4301-B5A6-B6CF18C1B320}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1099,7 +1108,7 @@
     Lack of convergence criteria</t>
       </text>
     </comment>
-    <comment ref="U206" authorId="111" shapeId="0" xr:uid="{0CF30255-8A3D-4919-9233-FFF88F64BDEC}">
+    <comment ref="U206" authorId="112" shapeId="0" xr:uid="{0CF30255-8A3D-4919-9233-FFF88F64BDEC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1107,7 +1116,7 @@
     Reported results regard unknown partition</t>
       </text>
     </comment>
-    <comment ref="AB206" authorId="112" shapeId="0" xr:uid="{7108276D-7BAD-4C60-8328-BCB059D3D8F0}">
+    <comment ref="AB206" authorId="113" shapeId="0" xr:uid="{7108276D-7BAD-4C60-8328-BCB059D3D8F0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1115,23 +1124,23 @@
     Crossval was used on training set for hyperparameters tuning, however tuned hyperparameters are not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q208" authorId="113" shapeId="0" xr:uid="{C5F1093F-9A67-46F1-BB46-E2ED57133E58}">
+    <comment ref="Q208" authorId="114" shapeId="0" xr:uid="{C5F1093F-9A67-46F1-BB46-E2ED57133E58}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Logistic Regression is trained over selected features. </t>
+    Linear Regression is trained over selected features. </t>
       </text>
     </comment>
-    <comment ref="U208" authorId="114" shapeId="0" xr:uid="{7E8CE905-D68B-46B6-BF95-92BB9D2FA33E}">
+    <comment ref="U208" authorId="115" shapeId="0" xr:uid="{7E8CE905-D68B-46B6-BF95-92BB9D2FA33E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    These results are for Logistic Regression with Pearson Correlation for features selection</t>
+    These results are for Linear Regression with Pearson Correlation for features selection</t>
       </text>
     </comment>
-    <comment ref="R210" authorId="115" shapeId="0" xr:uid="{95F9FDCB-C409-4D61-9B8E-6A459F2B95EA}">
+    <comment ref="R210" authorId="116" shapeId="0" xr:uid="{95F9FDCB-C409-4D61-9B8E-6A459F2B95EA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1139,7 +1148,7 @@
     We assume that term „evaluation” here relates to development set, since reported results regard test set.</t>
       </text>
     </comment>
-    <comment ref="P231" authorId="116" shapeId="0" xr:uid="{53A145EB-5B5C-43AF-8DE6-CF60C8320023}">
+    <comment ref="P231" authorId="117" shapeId="0" xr:uid="{53A145EB-5B5C-43AF-8DE6-CF60C8320023}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1147,7 +1156,7 @@
     Number of model layers is not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q231" authorId="117" shapeId="0" xr:uid="{2C5027EE-E875-4E68-BDE4-419515D07511}">
+    <comment ref="Q231" authorId="118" shapeId="0" xr:uid="{2C5027EE-E875-4E68-BDE4-419515D07511}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1155,7 +1164,7 @@
     Lack of training-related details (e.g. number of epochs. Optimization of layers number N is unclear: „best value N is determined from optimizing on heldout data” since „heldout data” refers to an unknown data partition</t>
       </text>
     </comment>
-    <comment ref="M242" authorId="118" shapeId="0" xr:uid="{3E8368AE-4C76-4EE5-9606-A227752F0E4D}">
+    <comment ref="M242" authorId="119" shapeId="0" xr:uid="{3E8368AE-4C76-4EE5-9606-A227752F0E4D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1163,7 +1172,7 @@
     Data preprocessing is not disclosed</t>
       </text>
     </comment>
-    <comment ref="O242" authorId="119" shapeId="0" xr:uid="{67041EBC-E75E-4F20-A731-06D3FD083A42}">
+    <comment ref="O242" authorId="120" shapeId="0" xr:uid="{67041EBC-E75E-4F20-A731-06D3FD083A42}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1171,7 +1180,7 @@
     Partitions disjoint level is not disclosed</t>
       </text>
     </comment>
-    <comment ref="P242" authorId="120" shapeId="0" xr:uid="{0E49BF83-321E-4A50-8AA1-E7AA54FCF4BF}">
+    <comment ref="P242" authorId="121" shapeId="0" xr:uid="{0E49BF83-321E-4A50-8AA1-E7AA54FCF4BF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1179,7 +1188,7 @@
     It’s unclear how a ResNet is applied to video modality, which in DAIC-WOZ does not consist of raw video but extracted features</t>
       </text>
     </comment>
-    <comment ref="R242" authorId="121" shapeId="0" xr:uid="{498C9FC9-A5A7-4224-B16F-D5EF190BF23C}">
+    <comment ref="R242" authorId="122" shapeId="0" xr:uid="{498C9FC9-A5A7-4224-B16F-D5EF190BF23C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1187,7 +1196,7 @@
     Some of the hyperparameters are optimized using grid search: „The selection of gamma and cost from the KELM model parameter is made by adopting a grid search technique [...]”, however the best model selection criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="U242" authorId="122" shapeId="0" xr:uid="{7B53DDEA-4529-4810-A667-A80E6935CBB7}">
+    <comment ref="U242" authorId="123" shapeId="0" xr:uid="{7B53DDEA-4529-4810-A667-A80E6935CBB7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1195,7 +1204,7 @@
     Inconsistencies between table 12 and fig 10. Reported metrics in two places differ by one order of magnitude. Therefore, we do not include these results in our table</t>
       </text>
     </comment>
-    <comment ref="M258" authorId="123" shapeId="0" xr:uid="{13E15B68-D8EB-453F-A440-8ADF91D209FE}">
+    <comment ref="M258" authorId="124" shapeId="0" xr:uid="{13E15B68-D8EB-453F-A440-8ADF91D209FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1203,7 +1212,7 @@
     Described data preprocessing is not applicable to DAIC-WOZ dataset</t>
       </text>
     </comment>
-    <comment ref="Q258" authorId="124" shapeId="0" xr:uid="{362F1E12-AE78-415F-A6CC-0AB28016237B}">
+    <comment ref="Q258" authorId="125" shapeId="0" xr:uid="{362F1E12-AE78-415F-A6CC-0AB28016237B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1211,7 +1220,7 @@
     Number of training epochs is not disclosed</t>
       </text>
     </comment>
-    <comment ref="R258" authorId="125" shapeId="0" xr:uid="{6431F48F-4542-493A-9EE5-316D908FE3DB}">
+    <comment ref="R258" authorId="126" shapeId="0" xr:uid="{6431F48F-4542-493A-9EE5-316D908FE3DB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1219,7 +1228,7 @@
     Convergence criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="N259" authorId="126" shapeId="0" xr:uid="{3E032A8A-B784-48B5-818D-94D4D4B26CD3}">
+    <comment ref="N259" authorId="127" shapeId="0" xr:uid="{3E032A8A-B784-48B5-818D-94D4D4B26CD3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1227,7 +1236,7 @@
     Data partitioning is not disclosed</t>
       </text>
     </comment>
-    <comment ref="P259" authorId="127" shapeId="0" xr:uid="{52E93B78-620B-48BF-B267-15F47AB8F619}">
+    <comment ref="P259" authorId="128" shapeId="0" xr:uid="{52E93B78-620B-48BF-B267-15F47AB8F619}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1235,7 +1244,7 @@
     Hyperparameters of the model are not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q259" authorId="128" shapeId="0" xr:uid="{74A938EB-68A3-4EE7-A92B-0CEFAABAEF51}">
+    <comment ref="Q259" authorId="129" shapeId="0" xr:uid="{74A938EB-68A3-4EE7-A92B-0CEFAABAEF51}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1243,7 +1252,7 @@
     Lack of training-related details (number of epochs, learning rate)</t>
       </text>
     </comment>
-    <comment ref="K276" authorId="129" shapeId="0" xr:uid="{106E5C7D-D279-41F4-B8E3-B8E09333BA76}">
+    <comment ref="K276" authorId="130" shapeId="0" xr:uid="{106E5C7D-D279-41F4-B8E3-B8E09333BA76}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1251,7 +1260,7 @@
     Page not exist</t>
       </text>
     </comment>
-    <comment ref="Q318" authorId="130" shapeId="0" xr:uid="{4E047EE5-FFE7-4206-9BFC-6B1D09F1CD6E}">
+    <comment ref="Q318" authorId="131" shapeId="0" xr:uid="{4E047EE5-FFE7-4206-9BFC-6B1D09F1CD6E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1259,7 +1268,7 @@
     Optimization method for DCGAN training is not disclosed</t>
       </text>
     </comment>
-    <comment ref="Q338" authorId="131" shapeId="0" xr:uid="{0C8FFD74-B105-4CAA-8C87-BA60A96B0B98}">
+    <comment ref="Q338" authorId="132" shapeId="0" xr:uid="{0C8FFD74-B105-4CAA-8C87-BA60A96B0B98}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1267,7 +1276,7 @@
     SGD training details is not disclosed</t>
       </text>
     </comment>
-    <comment ref="R338" authorId="132" shapeId="0" xr:uid="{3508F62D-E515-44FB-8EE2-0878A20159D0}">
+    <comment ref="R338" authorId="133" shapeId="0" xr:uid="{3508F62D-E515-44FB-8EE2-0878A20159D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1275,7 +1284,7 @@
     Best model selection criteria are not disclosed</t>
       </text>
     </comment>
-    <comment ref="E347" authorId="133" shapeId="0" xr:uid="{9B68B1A4-6F77-4C20-83B9-932BBA13DBFA}">
+    <comment ref="E347" authorId="134" shapeId="0" xr:uid="{9B68B1A4-6F77-4C20-83B9-932BBA13DBFA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1283,7 +1292,7 @@
     Number of papers with no decision provided yet due to the issues with retrieving the document</t>
       </text>
     </comment>
-    <comment ref="G347" authorId="134" shapeId="0" xr:uid="{9EE4B5EC-C74D-4ACE-A823-A5A9548E0488}">
+    <comment ref="G347" authorId="135" shapeId="0" xr:uid="{9EE4B5EC-C74D-4ACE-A823-A5A9548E0488}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1291,7 +1300,7 @@
     Does not regard DAIC-WOZ dataset </t>
       </text>
     </comment>
-    <comment ref="H347" authorId="135" shapeId="0" xr:uid="{2A88D3A4-3D01-4A31-9D88-4DB18487C5CC}">
+    <comment ref="H347" authorId="136" shapeId="0" xr:uid="{2A88D3A4-3D01-4A31-9D88-4DB18487C5CC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1300,7 +1309,7 @@
 (MAE) to assess estimation quality</t>
       </text>
     </comment>
-    <comment ref="I347" authorId="136" shapeId="0" xr:uid="{DA3EDAE9-AD1D-4518-A404-A0062D753D4F}">
+    <comment ref="I347" authorId="137" shapeId="0" xr:uid="{DA3EDAE9-AD1D-4518-A404-A0062D753D4F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1309,7 +1318,7 @@
 or repurpose an existing model</t>
       </text>
     </comment>
-    <comment ref="J347" authorId="137" shapeId="0" xr:uid="{4A25A468-1073-4BD0-9363-2EA8C91917EF}">
+    <comment ref="J347" authorId="138" shapeId="0" xr:uid="{4A25A468-1073-4BD0-9363-2EA8C91917EF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1317,7 +1326,7 @@
     Not in English</t>
       </text>
     </comment>
-    <comment ref="K347" authorId="138" shapeId="0" xr:uid="{AEABD4DE-B112-4A6A-9CEE-C655D1C68564}">
+    <comment ref="K347" authorId="139" shapeId="0" xr:uid="{AEABD4DE-B112-4A6A-9CEE-C655D1C68564}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1325,7 +1334,7 @@
     Records not retrieved during full text screening phase</t>
       </text>
     </comment>
-    <comment ref="N347" authorId="139" shapeId="0" xr:uid="{F8491903-E287-4F11-BBFA-AC518C5B5DF8}">
+    <comment ref="N347" authorId="140" shapeId="0" xr:uid="{F8491903-E287-4F11-BBFA-AC518C5B5DF8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1334,7 +1343,7 @@
 (MAE) to assess estimation quality</t>
       </text>
     </comment>
-    <comment ref="A348" authorId="140" shapeId="0" xr:uid="{B371964B-2AAC-4AC9-A5AE-70545583CE99}">
+    <comment ref="A348" authorId="141" shapeId="0" xr:uid="{B371964B-2AAC-4AC9-A5AE-70545583CE99}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1354,7 +1363,7 @@
     <author>tc={9517F61E-8098-4492-A4F1-E67F7A5866D4}</author>
     <author>tc={EF9FE58F-6167-4A1B-B82A-6CBDF41268F5}</author>
     <author>tc={B42F6DAD-BFC4-408B-92EB-2EE8848EB4FF}</author>
-    <author>tc={CAB99698-75FB-43D1-A3EB-8805AE913F7F}</author>
+    <author>tc={50F4A57F-C039-4279-8DAD-E91E4F6A4CCD}</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0" shapeId="0" xr:uid="{9517F61E-8098-4492-A4F1-E67F7A5866D4}">
@@ -1381,14 +1390,12 @@
     Irrelevant title and/or abstract</t>
       </text>
     </comment>
-    <comment ref="C7" authorId="3" shapeId="0" xr:uid="{CAB99698-75FB-43D1-A3EB-8805AE913F7F}">
+    <comment ref="D7" authorId="3" shapeId="0" xr:uid="{50F4A57F-C039-4279-8DAD-E91E4F6A4CCD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Records not retrieved
-Reply:
-    Number of records sought for retrieval is calculating by summing up „Accepted” and „Not retrieved”</t>
+    Records not retrieved.</t>
       </text>
     </comment>
   </commentList>
@@ -1396,7 +1403,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="957">
   <si>
     <t>Hierarchical Attention Transfer Networks for Depression Assessment from Speech</t>
   </si>
@@ -3768,9 +3775,6 @@
     <t>Included</t>
   </si>
   <si>
-    <t>Manually prepared features from text per interview may imply bias. Looks a bit similar to https://doi.org/10.1145/3133944.3133951 which was published year before</t>
-  </si>
-  <si>
     <t>Quality screening</t>
   </si>
   <si>
@@ -3810,9 +3814,6 @@
     <t xml:space="preserve">Topic-based feature selection </t>
   </si>
   <si>
-    <t>Topics extraction from Interviewer' responses was performed on entire DAIC corpus and not exclusively on training set. Strongly relies on Interviewer's responses</t>
-  </si>
-  <si>
     <t>Uses interviewer's prompts</t>
   </si>
   <si>
@@ -3948,9 +3949,6 @@
     <t>Lack of training process description. Lack of clear disclosure of the data partitioning. Inconsistencies in reported MAE values in tables with ones in the text</t>
   </si>
   <si>
-    <t>It’s not clear whether interviewer prompts are included in the context fed to GPT. Prompts are not disclosed</t>
-  </si>
-  <si>
     <t>V-A</t>
   </si>
   <si>
@@ -4095,9 +4093,6 @@
     <t>FaceHOG, Pearson Correlation for features selection</t>
   </si>
   <si>
-    <t>Logistic Regression</t>
-  </si>
-  <si>
     <t>Authors point out that "Due to the high dimensionality of the extracted features from videos, the complexity of the decision models built for depression detection is high. Also, it provides an overfitted learning model."</t>
   </si>
   <si>
@@ -4264,6 +4259,21 @@
   </si>
   <si>
     <t>Described video preprocessing is not applicable to DAIC-WOZ dataset, since the features are already extracted from video. BoW extraction from transcripts is vague. Exact dimensionalities and number of layers is not disclosed. Convergence and best model selection criteria are not disclosed. Training-related details are not disclosed (optimizer, learning rate, number of epochs etc). Convergence and best model selection criteria are not disclosed.</t>
+  </si>
+  <si>
+    <t>Interviewer utterance removal, participant utterance concatenation</t>
+  </si>
+  <si>
+    <t>Prompts are not disclosed</t>
+  </si>
+  <si>
+    <t>Grid search on train-val split is mentioned, however target metric used for best hyperparameter combination selection is not disclosed. Topics extraction from Interviewer' responses was performed on entire DAIC corpus and not exclusively on training set. Strongly relies on Interviewer's responses</t>
+  </si>
+  <si>
+    <t>Detailed model specifications (e.g. number of trees in random forest) are not disclosed. Manually prepared features from text per interview may imply bias. Looks a bit similar to https://doi.org/10.1145/3133944.3133951 which was published year before.</t>
+  </si>
+  <si>
+    <t>Linear Regression</t>
   </si>
 </sst>
 </file>
@@ -4387,7 +4397,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4423,6 +4433,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4530,9 +4543,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
@@ -4544,6 +4554,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4712,63 +4725,63 @@
       <calculatedColumnFormula>IF(OR(Table1[[#This Row],[Does not regard DAIC-WOZ]]=TRUE,Table1[[#This Row],[Does not use MAE]]=TRUE,Table1[[#This Row],[Does not introduce new model]]=TRUE,Table1[[#This Row],[Not in English]]=TRUE,Table1[[#This Row],[Not retrieved]]=TRUE),TRUE,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{CD629356-F203-4CD1-8C7D-29A17D970C26}" name="Data preprocessing" dataDxfId="49"/>
-    <tableColumn id="20" xr3:uid="{894681E3-7E9D-4747-A228-B0335307982D}" name="Data partitioning" totalsRowFunction="custom" dataDxfId="28" totalsRowDxfId="17">
+    <tableColumn id="20" xr3:uid="{894681E3-7E9D-4747-A228-B0335307982D}" name="Data partitioning" totalsRowFunction="custom" dataDxfId="48" totalsRowDxfId="17">
       <totalsRowFormula>COUNTIF(Table1[Data partitioning], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A332A605-56EF-4835-B8B4-2CA489A7AFB8}" name="Partitions disjoint level" totalsRowFunction="custom" dataDxfId="48" totalsRowDxfId="16">
+    <tableColumn id="19" xr3:uid="{A332A605-56EF-4835-B8B4-2CA489A7AFB8}" name="Partitions disjoint level" totalsRowFunction="custom" dataDxfId="47" totalsRowDxfId="16">
       <totalsRowFormula>COUNTIF(Table1[Partitions disjoint level], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{4C08AE79-ADCF-4117-9235-953496B61CFE}" name="Model description" totalsRowFunction="custom" dataDxfId="47" totalsRowDxfId="15">
+    <tableColumn id="18" xr3:uid="{4C08AE79-ADCF-4117-9235-953496B61CFE}" name="Model description" totalsRowFunction="custom" dataDxfId="46" totalsRowDxfId="15">
       <totalsRowFormula>COUNTIF(Table1[Model description], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{22D43059-EF48-46E7-861D-AA1D5830CC3E}" name="Training details" totalsRowFunction="custom" dataDxfId="46" totalsRowDxfId="14">
+    <tableColumn id="17" xr3:uid="{22D43059-EF48-46E7-861D-AA1D5830CC3E}" name="Training details" totalsRowFunction="custom" dataDxfId="45" totalsRowDxfId="14">
       <totalsRowFormula>COUNTIF(Table1[Training details], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{C010C063-17C6-4601-97B0-F473A7E0ED8A}" name="Final model selection" totalsRowFunction="custom" dataDxfId="45" totalsRowDxfId="13">
+    <tableColumn id="24" xr3:uid="{C010C063-17C6-4601-97B0-F473A7E0ED8A}" name="Final model selection" totalsRowFunction="custom" dataDxfId="44" totalsRowDxfId="13">
       <totalsRowFormula>COUNTIF(Table1[Final model selection], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{96D29E9D-B738-42A9-A484-CE824E12EA08}" name="-" totalsRowFunction="custom" dataDxfId="44" totalsRowDxfId="12">
+    <tableColumn id="23" xr3:uid="{96D29E9D-B738-42A9-A484-CE824E12EA08}" name="-" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="12">
       <totalsRowFormula>COUNTIF(Table1[-], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{425D64B1-F9DF-418E-9949-88C362E160FE}" name="Data modality" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="11">
+    <tableColumn id="22" xr3:uid="{425D64B1-F9DF-418E-9949-88C362E160FE}" name="Data modality" totalsRowFunction="custom" dataDxfId="42" totalsRowDxfId="11">
       <totalsRowFormula>COUNTIF(Table1[Data modality], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{421CDF98-9E39-4D4D-A87D-06967A41F943}" name="Dev. MAE" totalsRowFunction="custom" dataDxfId="42" totalsRowDxfId="10">
+    <tableColumn id="27" xr3:uid="{421CDF98-9E39-4D4D-A87D-06967A41F943}" name="Dev. MAE" totalsRowFunction="custom" dataDxfId="41" totalsRowDxfId="10">
       <totalsRowFormula>COUNTIF(Table1[Dev. MAE], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{AD5504E0-79F1-476C-884B-9E2DD01B3D27}" name="Dev. RMSE" totalsRowFunction="custom" dataDxfId="41" totalsRowDxfId="9">
+    <tableColumn id="26" xr3:uid="{AD5504E0-79F1-476C-884B-9E2DD01B3D27}" name="Dev. RMSE" totalsRowFunction="custom" dataDxfId="40" totalsRowDxfId="9">
       <totalsRowFormula>COUNTIF(Table1[Dev. RMSE], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{E9091248-191F-4342-BC88-3D354CD35730}" name="Dev. R2" totalsRowFunction="custom" dataDxfId="40" totalsRowDxfId="8">
+    <tableColumn id="25" xr3:uid="{E9091248-191F-4342-BC88-3D354CD35730}" name="Dev. R2" totalsRowFunction="custom" dataDxfId="39" totalsRowDxfId="8">
       <totalsRowFormula>COUNTIF(Table1[Dev. R2], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{C2E5B58C-2B3F-4560-A0FF-7E404413FF45}" name="Test. MAE" totalsRowFunction="custom" dataDxfId="39" totalsRowDxfId="7">
+    <tableColumn id="32" xr3:uid="{C2E5B58C-2B3F-4560-A0FF-7E404413FF45}" name="Test. MAE" totalsRowFunction="custom" dataDxfId="38" totalsRowDxfId="7">
       <totalsRowFormula>COUNTIF(Table1[Test. MAE], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{66067C71-5FC8-4084-8B28-4D2DA9F9A592}" name="Test. RMSE" totalsRowFunction="custom" dataDxfId="38" totalsRowDxfId="6">
+    <tableColumn id="31" xr3:uid="{66067C71-5FC8-4084-8B28-4D2DA9F9A592}" name="Test. RMSE" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="6">
       <totalsRowFormula>COUNTIF(Table1[Test. RMSE], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{8763841C-FBD1-493C-BFDB-6619AB317FAD}" name="Test. R2" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="5">
+    <tableColumn id="30" xr3:uid="{8763841C-FBD1-493C-BFDB-6619AB317FAD}" name="Test. R2" totalsRowFunction="custom" dataDxfId="36" totalsRowDxfId="5">
       <totalsRowFormula>COUNTIF(Table1[Test. R2], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{56C4D923-F9EA-428A-B3D5-15BE84E07E95}" name="Code available" totalsRowFunction="custom" dataDxfId="36" totalsRowDxfId="4">
+    <tableColumn id="29" xr3:uid="{56C4D923-F9EA-428A-B3D5-15BE84E07E95}" name="Code available" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="4">
       <totalsRowFormula>COUNTIF(Table1[Code available], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{5506C6B9-54B0-4FB5-99BC-099286F6DC05}" name="Repeated experiments" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="3">
+    <tableColumn id="33" xr3:uid="{5506C6B9-54B0-4FB5-99BC-099286F6DC05}" name="Repeated experiments" totalsRowFunction="custom" dataDxfId="34" totalsRowDxfId="3">
       <totalsRowFormula>COUNTIF(Table1[Repeated experiments], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{26A2744A-49E9-4009-A65C-2D65379339C8}" name="Uses interviewer's prompts" totalsRowFunction="custom" dataDxfId="34" totalsRowDxfId="2">
+    <tableColumn id="34" xr3:uid="{26A2744A-49E9-4009-A65C-2D65379339C8}" name="Uses interviewer's prompts" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="2">
       <totalsRowFormula>COUNTIF(Table1[Uses interviewer''s prompts], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{FFC92FCE-D380-4A60-8134-62F806EE9958}" name="Participant inter-partition leakage" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="1">
+    <tableColumn id="36" xr3:uid="{FFC92FCE-D380-4A60-8134-62F806EE9958}" name="Participant inter-partition leakage" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="1">
       <totalsRowFormula>COUNTIF(Table1[Participant inter-partition leakage], "-")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{335EF865-D157-4F55-B6B9-E0443694784E}" name="--" dataDxfId="32"/>
-    <tableColumn id="35" xr3:uid="{6B57A7B3-A989-4490-B3D9-072E4DB68254}" name="Included" totalsRowFunction="custom" dataDxfId="31">
+    <tableColumn id="28" xr3:uid="{335EF865-D157-4F55-B6B9-E0443694784E}" name="--" dataDxfId="31"/>
+    <tableColumn id="35" xr3:uid="{6B57A7B3-A989-4490-B3D9-072E4DB68254}" name="Included" totalsRowFunction="custom" dataDxfId="30">
       <calculatedColumnFormula>IF(NOT(Table1[[#This Row],[Data modality]] = ""), NOT(OR(Table1[[#This Row],[Data preprocessing]] = "-", Table1[[#This Row],[Data partitioning]] = "-", Table1[[#This Row],[Partitions disjoint level]] = "-", Table1[[#This Row],[Model description]] ="-", Table1[[#This Row],[Training details]] = "-", Table1[[#This Row],[Final model selection]] = "-", Table1[[#This Row],[Discarded after full-text review]])),"")</calculatedColumnFormula>
       <totalsRowFormula>COUNTIF(AF2:AF339, TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B69A742A-43C4-4B9D-8A4B-F8CE46B8F958}" name="Comment" dataDxfId="30" totalsRowDxfId="0"/>
+    <tableColumn id="16" xr3:uid="{B69A742A-43C4-4B9D-8A4B-F8CE46B8F958}" name="Comment" dataDxfId="29" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5059,6 +5072,12 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="Q6" dT="2025-09-09T17:32:26.31" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{A23B929B-1F88-420C-A8C6-6233EE7C8E8F}">
+    <text>Detailed model specifications (e.g. number of trees in random forest) are not disclosed.</text>
+  </threadedComment>
+  <threadedComment ref="R11" dT="2025-09-09T17:13:13.75" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{6EEC5CFA-B222-4CA3-925C-04E536C2B580}">
+    <text>Grid search on train-val split is mentioned, however target metric used for best hyperparameter combination selection is not disclosed.</text>
+  </threadedComment>
   <threadedComment ref="V14" dT="2025-04-02T19:27:49.46" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{373F542D-AF71-4660-BEC6-02DF05EBA826}">
     <text>There was only train/test split so we treat these „test” results as dev, since „test” split is not held-out</text>
   </threadedComment>
@@ -5125,11 +5144,8 @@
   <threadedComment ref="V51" dT="2025-04-02T20:11:10.10" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{B87D8D32-FF14-4B06-B8C9-9BB3CDF78D6C}">
     <text>There are inconsistencies in reported MAE values in tables with ones in the text, therefore we do not include them here</text>
   </threadedComment>
-  <threadedComment ref="M52" dT="2025-04-03T07:03:43.42" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{EA1EE393-2B0E-40FD-B221-08D0E86D83D0}">
-    <text>Vague description of transcripts preprocessing. It’s not clear whether interviewer prompts are included in the context fed to GPT</text>
-  </threadedComment>
   <threadedComment ref="Q52" dT="2025-04-03T07:05:06.16" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{DD6D54C5-6BC1-4E2F-A4DB-141BA1177A6C}">
-    <text>Prompts are not disclosed, but we put here N/A since the model is not actually trained</text>
+    <text>Prompts are not disclosed.</text>
   </threadedComment>
   <threadedComment ref="O59" dT="2025-04-03T19:17:34.98" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{4F75EA70-DAA7-467B-BD29-1E817F9F74F6}">
     <text>No clear information on disjoint level. There are mentions of „sentences” but no concise section regarding data preprocessing</text>
@@ -5481,10 +5497,10 @@
     <text>Crossval was used on training set for hyperparameters tuning, however tuned hyperparameters are not disclosed</text>
   </threadedComment>
   <threadedComment ref="Q208" dT="2025-04-11T16:01:29.20" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{C5F1093F-9A67-46F1-BB46-E2ED57133E58}">
-    <text xml:space="preserve">Logistic Regression is trained over selected features. </text>
+    <text xml:space="preserve">Linear Regression is trained over selected features. </text>
   </threadedComment>
   <threadedComment ref="U208" dT="2025-04-11T15:42:24.91" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{7E8CE905-D68B-46B6-BF95-92BB9D2FA33E}">
-    <text>These results are for Logistic Regression with Pearson Correlation for features selection</text>
+    <text>These results are for Linear Regression with Pearson Correlation for features selection</text>
   </threadedComment>
   <threadedComment ref="R210" dT="2025-04-11T17:17:08.50" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{95F9FDCB-C409-4D61-9B8E-6A459F2B95EA}">
     <text>We assume that term „evaluation” here relates to development set, since reported results regard test set.</text>
@@ -5584,11 +5600,8 @@
   <threadedComment ref="C5" dT="2025-04-01T16:30:43.70" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{B42F6DAD-BFC4-408B-92EB-2EE8848EB4FF}">
     <text>Irrelevant title and/or abstract</text>
   </threadedComment>
-  <threadedComment ref="C7" dT="2025-04-01T16:30:58.98" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{CAB99698-75FB-43D1-A3EB-8805AE913F7F}">
-    <text>Records not retrieved</text>
-  </threadedComment>
-  <threadedComment ref="C7" dT="2025-04-01T16:31:53.12" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{91DFE954-E372-4DC1-A233-6F7FADCC0480}" parentId="{CAB99698-75FB-43D1-A3EB-8805AE913F7F}">
-    <text>Number of records sought for retrieval is calculating by summing up „Accepted” and „Not retrieved”</text>
+  <threadedComment ref="D7" dT="2025-09-09T20:06:17.69" personId="{38AD1B54-1DAE-4F2A-AEAB-EA488571B049}" id="{50F4A57F-C039-4279-8DAD-E91E4F6A4CCD}">
+    <text>Records not retrieved.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -5710,10 +5723,10 @@
         <v>776</v>
       </c>
       <c r="AC1" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="AD1" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AE1" s="9" t="s">
         <v>762</v>
@@ -6021,7 +6034,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -6056,7 +6069,7 @@
         <v>785</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>777</v>
+        <v>753</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>787</v>
@@ -6098,10 +6111,10 @@
       <c r="AE6" s="1"/>
       <c r="AF6" s="1" t="b">
         <f>IF(NOT(Table1[[#This Row],[Data modality]] = ""), NOT(OR(Table1[[#This Row],[Data preprocessing]] = "-", Table1[[#This Row],[Data partitioning]] = "-", Table1[[#This Row],[Partitions disjoint level]] = "-", Table1[[#This Row],[Model description]] ="-", Table1[[#This Row],[Training details]] = "-", Table1[[#This Row],[Final model selection]] = "-", Table1[[#This Row],[Discarded after full-text review]])),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="s">
-        <v>790</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -6227,16 +6240,16 @@
         <v>0</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>796</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>788</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>753</v>
@@ -6284,7 +6297,7 @@
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -6341,7 +6354,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -6364,22 +6377,22 @@
         <v>0</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>788</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>777</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>801</v>
+        <v>753</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1" t="s">
@@ -6418,10 +6431,10 @@
       <c r="AE11" s="1"/>
       <c r="AF11" s="1" t="b">
         <f>IF(NOT(Table1[[#This Row],[Data modality]] = ""), NOT(OR(Table1[[#This Row],[Data preprocessing]] = "-", Table1[[#This Row],[Data partitioning]] = "-", Table1[[#This Row],[Partitions disjoint level]] = "-", Table1[[#This Row],[Model description]] ="-", Table1[[#This Row],[Training details]] = "-", Table1[[#This Row],[Final model selection]] = "-", Table1[[#This Row],[Discarded after full-text review]])),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="s">
-        <v>804</v>
+        <v>954</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -6553,22 +6566,22 @@
         <v>0</v>
       </c>
       <c r="M14" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="O14" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>810</v>
       </c>
       <c r="S14" s="1"/>
       <c r="T14" s="1" t="s">
@@ -6610,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -6689,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>753</v>
@@ -6698,13 +6711,13 @@
         <v>788</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>753</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1" t="s">
@@ -6746,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -6781,7 +6794,7 @@
         <v>753</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>753</v>
@@ -6829,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="AG17" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -6917,7 +6930,7 @@
         <v>753</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>753</v>
@@ -6965,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -7043,7 +7056,7 @@
         <v>753</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>753</v>
@@ -7097,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="AG21" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="58" hidden="1" x14ac:dyDescent="0.35">
@@ -7126,7 +7139,7 @@
         <v>753</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>753</v>
@@ -7151,7 +7164,7 @@
         <v>5.0199999999999996</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="X22" s="1" t="s">
         <v>753</v>
@@ -7180,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="23" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -7253,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>779</v>
@@ -7262,7 +7275,7 @@
         <v>788</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>753</v>
@@ -7310,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="AG24" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="58" hidden="1" x14ac:dyDescent="0.35">
@@ -7336,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>753</v>
@@ -7345,7 +7358,7 @@
         <v>753</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>753</v>
@@ -7393,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="AG25" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="87" hidden="1" x14ac:dyDescent="0.35">
@@ -7419,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>779</v>
@@ -7428,17 +7441,17 @@
         <v>788</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>753</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="S26" s="1"/>
       <c r="T26" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U26" s="1">
         <v>2.94</v>
@@ -7476,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="AG26" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -7549,16 +7562,16 @@
         <v>0</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>753</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>777</v>
@@ -7568,7 +7581,7 @@
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U28" s="1" t="s">
         <v>753</v>
@@ -7606,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="AG28" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="29" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -8014,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>779</v>
@@ -8023,13 +8036,13 @@
         <v>766</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="Q37" s="1" t="s">
         <v>753</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1" t="s">
@@ -8071,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="38" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -8144,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>779</v>
@@ -8153,29 +8166,29 @@
         <v>788</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1" t="s">
         <v>770</v>
       </c>
       <c r="U39" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="X39" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="V39" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="W39" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>840</v>
       </c>
       <c r="Y39" s="1" t="s">
         <v>753</v>
@@ -8201,7 +8214,7 @@
         <v>1</v>
       </c>
       <c r="AG39" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="40" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
@@ -8415,16 +8428,16 @@
         <v>0</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="N44" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="O44" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>843</v>
-      </c>
       <c r="P44" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="Q44" s="1" t="s">
         <v>753</v>
@@ -8472,7 +8485,7 @@
         <v>0</v>
       </c>
       <c r="AG44" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="45" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -8780,16 +8793,16 @@
         <v>0</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>753</v>
       </c>
       <c r="O51" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="P51" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>848</v>
       </c>
       <c r="Q51" s="1" t="s">
         <v>753</v>
@@ -8835,10 +8848,10 @@
         <v>0</v>
       </c>
       <c r="AG51" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="52" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>152</v>
       </c>
@@ -8861,7 +8874,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>753</v>
+        <v>952</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>779</v>
@@ -8870,10 +8883,10 @@
         <v>788</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>787</v>
+        <v>753</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>787</v>
@@ -8918,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="AG52" t="s">
-        <v>850</v>
+        <v>953</v>
       </c>
     </row>
     <row r="53" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -9229,7 +9242,7 @@
         <v>753</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="Q59" s="1" t="s">
         <v>753</v>
@@ -9239,7 +9252,7 @@
       </c>
       <c r="S59" s="1"/>
       <c r="T59" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="U59" s="1" t="s">
         <v>753</v>
@@ -9277,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="AG59" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="60" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -9428,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>779</v>
@@ -9437,17 +9450,17 @@
         <v>788</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="Q63" s="1" t="s">
         <v>777</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S63" s="1"/>
       <c r="T63" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="U63" s="1">
         <v>5.5</v>
@@ -9485,7 +9498,7 @@
         <v>1</v>
       </c>
       <c r="AG63" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="64" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -9606,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="AG65" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="66" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -12236,7 +12249,7 @@
         <v>788</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="Q127" s="1" t="s">
         <v>753</v>
@@ -12284,7 +12297,7 @@
         <v>0</v>
       </c>
       <c r="AG127" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="128" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -12448,7 +12461,7 @@
         <v>753</v>
       </c>
       <c r="P131" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="Q131" s="1" t="s">
         <v>777</v>
@@ -12496,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="AG131" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="132" spans="1:33" ht="58" hidden="1" x14ac:dyDescent="0.35">
@@ -12761,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="AG136" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
     </row>
     <row r="137" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -12874,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="N139" s="1" t="s">
         <v>779</v>
@@ -12883,13 +12896,13 @@
         <v>788</v>
       </c>
       <c r="P139" s="1" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="Q139" s="1" t="s">
         <v>753</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="S139" s="1"/>
       <c r="T139" s="1" t="s">
@@ -12929,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="AG139" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="140" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -13041,7 +13054,7 @@
         <v>0</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="N142" s="1" t="s">
         <v>753</v>
@@ -13098,7 +13111,7 @@
         <v>0</v>
       </c>
       <c r="AG142" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="143" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -13176,7 +13189,7 @@
         <v>753</v>
       </c>
       <c r="P144" s="1" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="Q144" s="1" t="s">
         <v>777</v>
@@ -13186,7 +13199,7 @@
       </c>
       <c r="S144" s="1"/>
       <c r="T144" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U144" s="1">
         <v>4.6500000000000004</v>
@@ -13224,7 +13237,7 @@
         <v>0</v>
       </c>
       <c r="AG144" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="145" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -13474,22 +13487,22 @@
         <v>0</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="O150" s="1" t="s">
         <v>788</v>
       </c>
       <c r="P150" s="1" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="Q150" s="1" t="s">
         <v>777</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="S150" s="1"/>
       <c r="T150" s="1" t="s">
@@ -13531,7 +13544,7 @@
         <v>1</v>
       </c>
       <c r="AG150" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="151" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -13563,7 +13576,7 @@
         <v>788</v>
       </c>
       <c r="P151" s="1" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="Q151" s="1" t="s">
         <v>753</v>
@@ -13611,7 +13624,7 @@
         <v>0</v>
       </c>
       <c r="AG151" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="152" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -13766,16 +13779,16 @@
         <v>0</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="N155" s="1" t="s">
         <v>779</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="P155" s="1" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="Q155" s="1" t="s">
         <v>777</v>
@@ -13823,7 +13836,7 @@
         <v>0</v>
       </c>
       <c r="AG155" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="156" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
@@ -13994,13 +14007,13 @@
         <v>788</v>
       </c>
       <c r="P159" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Q159" s="1" t="s">
         <v>777</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="S159" s="1"/>
       <c r="T159" s="1" t="s">
@@ -14042,7 +14055,7 @@
         <v>0</v>
       </c>
       <c r="AG159" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
     </row>
     <row r="160" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -14113,7 +14126,7 @@
         <v>0</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="N161" s="1" t="s">
         <v>753</v>
@@ -14122,7 +14135,7 @@
         <v>788</v>
       </c>
       <c r="P161" s="1" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="Q161" s="1" t="s">
         <v>753</v>
@@ -14170,7 +14183,7 @@
         <v>0</v>
       </c>
       <c r="AG161" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="162" spans="1:33" ht="87" hidden="1" x14ac:dyDescent="0.35">
@@ -14193,22 +14206,22 @@
         <v>0</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O162" s="1" t="s">
         <v>788</v>
       </c>
       <c r="P162" s="1" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="Q162" s="1" t="s">
         <v>753</v>
       </c>
       <c r="R162" s="1" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="S162" s="1"/>
       <c r="T162" s="1" t="s">
@@ -14250,7 +14263,7 @@
         <v>0</v>
       </c>
       <c r="AG162" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
     </row>
     <row r="163" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -14552,7 +14565,7 @@
         <v>0</v>
       </c>
       <c r="AG168" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="169" spans="1:33" ht="58" hidden="1" x14ac:dyDescent="0.35">
@@ -14578,7 +14591,7 @@
         <v>753</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>753</v>
@@ -14630,7 +14643,7 @@
         <v>0</v>
       </c>
       <c r="AG169" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
     </row>
     <row r="170" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -14653,7 +14666,7 @@
         <v>0</v>
       </c>
       <c r="M170" s="1" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="N170" s="1" t="s">
         <v>779</v>
@@ -14662,7 +14675,7 @@
         <v>753</v>
       </c>
       <c r="P170" s="1" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="Q170" s="1" t="s">
         <v>753</v>
@@ -14672,7 +14685,7 @@
       </c>
       <c r="S170" s="1"/>
       <c r="T170" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U170" s="1">
         <v>3.75</v>
@@ -14710,7 +14723,7 @@
         <v>0</v>
       </c>
       <c r="AG170" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
     </row>
     <row r="171" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -14742,7 +14755,7 @@
         <v>753</v>
       </c>
       <c r="P171" s="1" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="Q171" s="1" t="s">
         <v>753</v>
@@ -14790,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="AG171" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
     </row>
     <row r="172" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -14857,7 +14870,7 @@
         <v>0</v>
       </c>
       <c r="M173" s="1" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="N173" s="1" t="s">
         <v>779</v>
@@ -14914,7 +14927,7 @@
         <v>0</v>
       </c>
       <c r="AG173" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="174" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -14981,7 +14994,7 @@
         <v>0</v>
       </c>
       <c r="M175" s="1" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="N175" s="1" t="s">
         <v>779</v>
@@ -15000,7 +15013,7 @@
       </c>
       <c r="S175" s="1"/>
       <c r="T175" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U175" s="1">
         <v>3</v>
@@ -15038,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="AG175" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="176" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -15067,10 +15080,10 @@
         <v>779</v>
       </c>
       <c r="O176" s="1" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="P176" s="1" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="Q176" s="1" t="s">
         <v>753</v>
@@ -15080,7 +15093,7 @@
       </c>
       <c r="S176" s="1"/>
       <c r="T176" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="U176" s="1" t="s">
         <v>753</v>
@@ -15118,7 +15131,7 @@
         <v>0</v>
       </c>
       <c r="AG176" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="177" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
@@ -15276,16 +15289,16 @@
         <v>0</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>788</v>
       </c>
       <c r="P180" s="1" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="Q180" s="1" t="s">
         <v>753</v>
@@ -15295,7 +15308,7 @@
       </c>
       <c r="S180" s="1"/>
       <c r="T180" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="U180" s="1" t="s">
         <v>753</v>
@@ -15333,7 +15346,7 @@
         <v>0</v>
       </c>
       <c r="AG180" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="181" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -15589,7 +15602,7 @@
         <v>753</v>
       </c>
       <c r="P186" s="1" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="Q186" s="1" t="s">
         <v>753</v>
@@ -15637,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="AG186" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="187" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -15704,7 +15717,7 @@
         <v>0</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="N188" s="1" t="s">
         <v>753</v>
@@ -15761,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="AG188" s="12" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
     <row r="189" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -16004,7 +16017,7 @@
         <v>0</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="N194" s="1" t="s">
         <v>779</v>
@@ -16013,7 +16026,7 @@
         <v>788</v>
       </c>
       <c r="P194" s="1" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="Q194" s="1" t="s">
         <v>753</v>
@@ -16573,16 +16586,16 @@
         <v>0</v>
       </c>
       <c r="M206" s="1" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="N206" s="1" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="O206" s="1" t="s">
         <v>788</v>
       </c>
       <c r="P206" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="Q206" s="1" t="s">
         <v>753</v>
@@ -16630,7 +16643,7 @@
         <v>0</v>
       </c>
       <c r="AG206" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="207" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -16697,7 +16710,7 @@
         <v>0</v>
       </c>
       <c r="M208" s="1" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="N208" s="1" t="s">
         <v>779</v>
@@ -16706,7 +16719,7 @@
         <v>788</v>
       </c>
       <c r="P208" s="1" t="s">
-        <v>899</v>
+        <v>956</v>
       </c>
       <c r="Q208" s="1" t="s">
         <v>787</v>
@@ -16754,7 +16767,7 @@
         <v>1</v>
       </c>
       <c r="AG208" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="209" spans="1:33" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -16821,7 +16834,7 @@
         <v>0</v>
       </c>
       <c r="M210" s="1" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="N210" s="1" t="s">
         <v>779</v>
@@ -16830,13 +16843,13 @@
         <v>788</v>
       </c>
       <c r="P210" s="1" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="Q210" s="1" t="s">
         <v>777</v>
       </c>
       <c r="R210" s="1" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="S210" s="1"/>
       <c r="T210" s="1" t="s">
@@ -16878,7 +16891,7 @@
         <v>1</v>
       </c>
       <c r="AG210" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="211" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -17796,13 +17809,13 @@
         <v>0</v>
       </c>
       <c r="M231" s="1" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="N231" s="1" t="s">
         <v>779</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="P231" s="1" t="s">
         <v>753</v>
@@ -17811,7 +17824,7 @@
         <v>753</v>
       </c>
       <c r="R231" s="1" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="S231" s="1"/>
       <c r="T231" s="1" t="s">
@@ -17853,7 +17866,7 @@
         <v>0</v>
       </c>
       <c r="AG231" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="232" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -18333,7 +18346,7 @@
         <v>753</v>
       </c>
       <c r="N242" s="1" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="O242" s="1" t="s">
         <v>753</v>
@@ -18385,7 +18398,7 @@
         <v>0</v>
       </c>
       <c r="AG242" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="243" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -19105,7 +19118,7 @@
         <v>788</v>
       </c>
       <c r="P258" s="1" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="Q258" s="1" t="s">
         <v>753</v>
@@ -19153,7 +19166,7 @@
         <v>0</v>
       </c>
       <c r="AG258" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="259" spans="1:33" ht="116" hidden="1" x14ac:dyDescent="0.35">
@@ -19176,7 +19189,7 @@
         <v>0</v>
       </c>
       <c r="M259" s="1" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="N259" s="1" t="s">
         <v>753</v>
@@ -19191,7 +19204,7 @@
         <v>753</v>
       </c>
       <c r="R259" s="1" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="S259" s="1"/>
       <c r="T259" s="1" t="s">
@@ -19233,7 +19246,7 @@
         <v>0</v>
       </c>
       <c r="AG259" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="260" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -19522,7 +19535,7 @@
         <v>0</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="G266" s="1" t="b">
         <v>1</v>
@@ -21884,7 +21897,7 @@
         <v>0</v>
       </c>
       <c r="M318" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="N318" s="1" t="s">
         <v>779</v>
@@ -21893,13 +21906,13 @@
         <v>766</v>
       </c>
       <c r="P318" s="1" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="Q318" s="1" t="s">
         <v>753</v>
       </c>
       <c r="R318" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="S318" s="1"/>
       <c r="T318" s="1" t="s">
@@ -21941,7 +21954,7 @@
         <v>0</v>
       </c>
       <c r="AG318" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
     </row>
     <row r="319" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -22796,13 +22809,13 @@
     </row>
     <row r="338" spans="1:33" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B338" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="B338" s="7" t="s">
+      <c r="C338" t="s">
         <v>799</v>
-      </c>
-      <c r="C338" t="s">
-        <v>800</v>
       </c>
       <c r="E338" s="1" t="b">
         <v>0</v>
@@ -22814,7 +22827,7 @@
         <v>0</v>
       </c>
       <c r="M338" s="1" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="N338" s="1" t="s">
         <v>779</v>
@@ -22823,13 +22836,13 @@
         <v>788</v>
       </c>
       <c r="P338" s="1" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="Q338" s="1" t="s">
         <v>753</v>
       </c>
       <c r="R338" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="S338" s="1"/>
       <c r="T338" s="1" t="s">
@@ -22871,7 +22884,7 @@
         <v>0</v>
       </c>
       <c r="AG338" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="339" spans="1:33" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -23276,11 +23289,11 @@
       </c>
       <c r="Q347" s="1">
         <f>COUNTIF(Table1[Training details], "-")</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R347" s="1">
         <f>COUNTIF(Table1[Final model selection], "-")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S347" s="1">
         <f>COUNTIF(Table1[-], "-")</f>
@@ -23332,7 +23345,7 @@
       </c>
       <c r="AF347">
         <f>COUNTIF(AF2:AF339, TRUE)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG347" s="1"/>
     </row>
@@ -23353,10 +23366,10 @@
     </row>
     <row r="352" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A352" s="14" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B352" s="15" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -23688,7 +23701,7 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C2" s="11">
         <v>45747</v>
@@ -23736,7 +23749,7 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C3">
         <f>(Stats!$E$6)/($P$2-C2-1)</f>
@@ -23794,7 +23807,7 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="C2:O2">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>C2=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23829,7 +23842,7 @@
         <v>719</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
@@ -23837,7 +23850,7 @@
         <v>718</v>
       </c>
       <c r="C3" s="16">
-        <f>SUM(C4:C7) - C7</f>
+        <f>C4+C5+C6</f>
         <v>345</v>
       </c>
       <c r="D3" s="16">
@@ -23858,16 +23871,16 @@
         <v>108</v>
       </c>
       <c r="D4" s="16">
-        <f>D3-D5</f>
+        <f>D3-D5-D7</f>
         <v>56</v>
       </c>
       <c r="E4" s="16">
         <f>COUNTIF(Screening!AF2:AF339, TRUE)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="13">
         <f>E4/E3</f>
-        <v>0.125</v>
+        <v>8.9285714285714288E-2</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
@@ -23879,16 +23892,16 @@
         <v>237</v>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIF(Table1[Discarded after full-text review], TRUE)</f>
-        <v>52</v>
+        <f>COUNTIF(Table1[Discarded after full-text review], TRUE) - D7</f>
+        <v>50</v>
       </c>
       <c r="E5" s="16">
         <f>COUNTIF(Screening!AF2:AF339, FALSE)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" s="13">
         <f>E5/E3</f>
-        <v>0.875</v>
+        <v>0.9107142857142857</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
@@ -23900,7 +23913,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="16">
-        <f>D3-D4-D5</f>
+        <f>D3-D4-D5-D7</f>
         <v>0</v>
       </c>
       <c r="E6" s="16">
@@ -23916,14 +23929,14 @@
       <c r="B7" s="16" t="s">
         <v>746</v>
       </c>
-      <c r="C7" s="16">
-        <f>COUNTIF(Table1[Irrelevant title/abstract], "?")+COUNTIF(Table1[Not retrieved], TRUE)</f>
+      <c r="C7" s="17" t="s">
+        <v>787</v>
+      </c>
+      <c r="D7" s="16">
+        <f>COUNTIF(Table1[Not retrieved], TRUE)</f>
         <v>2</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>787</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="17" t="s">
         <v>787</v>
       </c>
     </row>

--- a/paper/screening.xlsx
+++ b/paper/screening.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WL961KX\Private\MSc\Thesis\Systematic Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA9221B-CDC6-4153-B579-6560372AA4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C265100-DE73-4C5A-95BF-053EE612F169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="957">
   <si>
     <t>Hierarchical Attention Transfer Networks for Depression Assessment from Speech</t>
   </si>
@@ -4283,7 +4283,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-415]d\ mmm;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4340,13 +4340,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -8832,7 +8825,9 @@
       <c r="Z51" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="AA51" s="1"/>
+      <c r="AA51" s="1" t="s">
+        <v>773</v>
+      </c>
       <c r="AB51" s="1" t="s">
         <v>773</v>
       </c>
@@ -12929,7 +12924,9 @@
       <c r="AA139" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="AB139" s="1"/>
+      <c r="AB139" s="1" t="s">
+        <v>773</v>
+      </c>
       <c r="AC139" s="1" t="s">
         <v>773</v>
       </c>

--- a/paper/screening.xlsx
+++ b/paper/screening.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WL961KX\Private\MSc\Thesis\Systematic Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C265100-DE73-4C5A-95BF-053EE612F169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8C5ACA-D61E-4283-861A-E2B0D2F6D5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="957">
   <si>
     <t>Hierarchical Attention Transfer Networks for Depression Assessment from Speech</t>
   </si>
@@ -14552,7 +14552,9 @@
       <c r="AB168" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="AC168" s="1"/>
+      <c r="AC168" s="1" t="s">
+        <v>753</v>
+      </c>
       <c r="AD168" s="1" t="s">
         <v>773</v>
       </c>
@@ -14599,7 +14601,9 @@
       <c r="Q169" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="R169" s="1"/>
+      <c r="R169" s="1" t="s">
+        <v>753</v>
+      </c>
       <c r="S169" s="1"/>
       <c r="T169" s="1" t="s">
         <v>770</v>
@@ -18354,7 +18358,9 @@
       <c r="Q242" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="R242" s="1"/>
+      <c r="R242" s="1" t="s">
+        <v>753</v>
+      </c>
       <c r="S242" s="1"/>
       <c r="T242" s="1" t="s">
         <v>784</v>
@@ -23290,7 +23296,7 @@
       </c>
       <c r="R347" s="1">
         <f>COUNTIF(Table1[Final model selection], "-")</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S347" s="1">
         <f>COUNTIF(Table1[-], "-")</f>
@@ -23334,7 +23340,7 @@
       </c>
       <c r="AC347" s="1">
         <f>COUNTIF(Table1[Uses interviewer''s prompts], "-")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD347" s="1">
         <f>COUNTIF(Table1[Participant inter-partition leakage], "-")</f>
